--- a/Unity/Assets/Config/Excel/LevelConfig.xlsx
+++ b/Unity/Assets/Config/Excel/LevelConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -38,6 +38,9 @@
     <t>LevelName</t>
   </si>
   <si>
+    <t>SceneName</t>
+  </si>
+  <si>
     <t>WaveIds</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
     <t>关卡名称</t>
   </si>
   <si>
+    <t>地图名称</t>
+  </si>
+  <si>
     <t>波</t>
   </si>
   <si>
@@ -69,6 +75,9 @@
   </si>
   <si>
     <t>关卡1-1</t>
+  </si>
+  <si>
+    <t>Level_1</t>
   </si>
   <si>
     <t>1001,1002,1003</t>
@@ -1110,17 +1119,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
-    <col min="2" max="3" width="17.875" style="2"/>
-    <col min="4" max="4" width="19.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.375" style="2" customWidth="1"/>
-    <col min="6" max="16383" width="17.875" style="2"/>
+    <col min="2" max="4" width="17.875" style="2"/>
+    <col min="5" max="5" width="19.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1136,80 +1145,98 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:5">
+    <row r="4" customHeight="1" spans="2:6">
       <c r="B4" s="2">
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:5">
+    <row r="5" customHeight="1" spans="2:6">
       <c r="B5" s="2">
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:5">
+    <row r="6" customHeight="1" spans="2:6">
       <c r="B6" s="2">
         <v>201</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="E6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="2">
         <v>500</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/LevelConfig.xlsx
+++ b/Unity/Assets/Config/Excel/LevelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="22185" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -80,13 +80,19 @@
     <t>Level_1</t>
   </si>
   <si>
-    <t>1001,1002,1003</t>
+    <t>10101,10102,10103</t>
   </si>
   <si>
     <t>关卡1-2</t>
   </si>
   <si>
+    <t>10201,10202,10203</t>
+  </si>
+  <si>
     <t>关卡2-1</t>
+  </si>
+  <si>
+    <t>20101,20102</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1223,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2">
         <v>500</v>
@@ -1228,13 +1234,13 @@
         <v>201</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2">
         <v>500</v>

--- a/Unity/Assets/Config/Excel/LevelConfig.xlsx
+++ b/Unity/Assets/Config/Excel/LevelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22185" windowHeight="9555"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,13 +80,13 @@
     <t>Level_1</t>
   </si>
   <si>
-    <t>10101,10102,10103</t>
+    <t>10101,10102,10103,10104,10105,10106</t>
   </si>
   <si>
     <t>关卡1-2</t>
   </si>
   <si>
-    <t>10201,10202,10203</t>
+    <t>10201,10202,10203,10204,10205,10206</t>
   </si>
   <si>
     <t>关卡2-1</t>
@@ -1130,7 +1130,7 @@
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="4" width="17.875" style="2"/>
-    <col min="5" max="5" width="19.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="51.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.375" style="2" customWidth="1"/>
     <col min="7" max="16384" width="17.875" style="2"/>
   </cols>

--- a/Unity/Assets/Config/Excel/LevelConfig.xlsx
+++ b/Unity/Assets/Config/Excel/LevelConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>##var</t>
   </si>
@@ -38,9 +38,6 @@
     <t>LevelName</t>
   </si>
   <si>
-    <t>SceneName</t>
-  </si>
-  <si>
     <t>WaveIds</t>
   </si>
   <si>
@@ -65,9 +62,6 @@
     <t>关卡名称</t>
   </si>
   <si>
-    <t>地图名称</t>
-  </si>
-  <si>
     <t>波</t>
   </si>
   <si>
@@ -75,9 +69,6 @@
   </si>
   <si>
     <t>关卡1-1</t>
-  </si>
-  <si>
-    <t>Level_1</t>
   </si>
   <si>
     <t>10101,10102,10103,10104,10105,10106</t>
@@ -1125,17 +1116,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
-    <col min="2" max="4" width="17.875" style="2"/>
-    <col min="5" max="5" width="51.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="17.875" style="2"/>
+    <col min="2" max="3" width="17.875" style="2"/>
+    <col min="4" max="4" width="51.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.375" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1151,98 +1142,80 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="4" customHeight="1" spans="2:6">
+    <row r="4" customHeight="1" spans="2:5">
       <c r="B4" s="2">
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:6">
+    <row r="5" customHeight="1" spans="2:5">
       <c r="B5" s="2">
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="E5" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:6">
+    <row r="6" customHeight="1" spans="2:5">
       <c r="B6" s="2">
         <v>201</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="2">
+        <v>17</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2">
         <v>500</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/LevelConfig.xlsx
+++ b/Unity/Assets/Config/Excel/LevelConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
     <t>关卡2-1</t>
   </si>
   <si>
-    <t>20101,20102</t>
+    <t>20101,20102,20103,20104,20105,20106</t>
   </si>
 </sst>
 </file>
